--- a/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$465</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$465</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$413</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E416"/>
+  <dimension ref="A1:E413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4279,7 +4279,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PE1018</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4289,24 +4289,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>30 ord: - förstå förskolans och skolans samhällsuppdrag i förhållande till hur man bemöt…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>PE1018</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur samverkan kan utvecklas mellan barn och elever i förhållande …</t>
+          <t>31 ord: - är medveten om att han/hon är en myndighetsperson, dvs. kan hantera arbetsrela…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - kan visa hur han/hon arbetar aktivt i linje med högskolelagens/förordningens f…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>31 ord: - är medveten om att han/hon är en myndighetsperson, dvs. kan hantera arbetsrela…</t>
+          <t>41 ord: - kan analysera och diskutera studenters lärande i högre utbildning med hjälp av…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>27 ord: - kan visa hur han/hon arbetar aktivt i linje med högskolelagens/förordningens f…</t>
+          <t>26 ord: - kan påvisa yttringar av lärandet hos studenter och hos sig själv och koppla de…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>41 ord: - kan analysera och diskutera studenters lärande i högre utbildning med hjälp av…</t>
+          <t>36 ord: - inom det egna kunskapsområdet kan formulera mål och förväntade studieresultat,…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>26 ord: - kan påvisa yttringar av lärandet hos studenter och hos sig själv och koppla de…</t>
+          <t>32 ord: - kan beskriva, analysera och diskutera egna och andras erfarenheter genom jämfö…</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>36 ord: - inom det egna kunskapsområdet kan formulera mål och förväntade studieresultat,…</t>
+          <t>28 ord: - kan planera och genomföra, redovisa och med kollegor diskutera ett självständi…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE1032</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4505,24 +4505,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>32 ord: - kan beskriva, analysera och diskutera egna och andras erfarenheter genom jämfö…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE1050</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>28 ord: - kan planera och genomföra, redovisa och med kollegor diskutera ett självständi…</t>
+          <t>40 ord: - redogöra för och diskutera förskolans och skolans samhällsuppdrag i förhålland…</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>PE1032</t>
+          <t>PE1050</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4559,17 +4559,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>27 ord: - visa förmåga att omsätta teoretisk kunskap i planering och genomförande av ped…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>40 ord: - redogöra för och diskutera förskolans och skolans samhällsuppdrag i förhålland…</t>
+          <t>35 ord: - redogöra för och diskutera hur samverkan kan utvecklas mellan barn och elever …</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att omsätta teoretisk kunskap i planering och genomförande av ped…</t>
+          <t>27 ord: - redogöra för och diskutera olika tolkningar av hur förskolans och skolans peda…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PE1050</t>
+          <t>PE1053</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4640,24 +4640,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för och diskutera hur samverkan kan utvecklas mellan barn och elever …</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PE1050</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för och diskutera olika tolkningar av hur förskolans och skolans peda…</t>
+          <t>37 ord: - använda pedagogisk dokumentation som underlag för att tillsammans med kollegor…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PE1053</t>
+          <t>PE1055</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
+          <t>38 ord: - beskriva, dokumentera och analysera möjligheter och hinder i förskolans verksa…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>PE1056</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>37 ord: - använda pedagogisk dokumentation som underlag för att tillsammans med kollegor…</t>
+          <t>26 ord: - identifiera och reflektera över vad det innebär att planera, följa upp, utvärd…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PE1055</t>
+          <t>PE1056</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4753,19 +4753,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva, dokumentera och analysera möjligheter och hinder i förskolans verksa…</t>
+          <t>26 ord: - beskriva och analysera hur förskolechefen kan planera och leda arbetsprocesser…</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PE1056</t>
+          <t>PE1060</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4775,24 +4775,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>26 ord: - identifiera och reflektera över vad det innebär att planera, följa upp, utvärd…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PE1056</t>
+          <t>PE1070</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>26 ord: - beskriva och analysera hur förskolechefen kan planera och leda arbetsprocesser…</t>
+          <t>26 ord: - visa kunskap om vilka steg som bör tas för att bygga upp organisationen i form…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PE1060</t>
+          <t>PE1074</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4829,24 +4829,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>32 ord: - ha insikt i lärplattans möjligheter och begränsningar i arbetet med yngre elev…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PE1070</t>
+          <t>PE2007</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4856,24 +4856,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om vilka steg som bör tas för att bygga upp organisationen i form…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>PE1074</t>
+          <t>PE2017</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>32 ord: - ha insikt i lärplattans möjligheter och begränsningar i arbetet med yngre elev…</t>
+          <t>28 ord: - skriftligt och muntligt kritiskt granska och argumentera för och emot hur olik…</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>PE2007</t>
+          <t>PE3002</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4915,19 +4915,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>PE2017</t>
+          <t>PE3003</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4937,24 +4937,24 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>28 ord: - skriftligt och muntligt kritiskt granska och argumentera för och emot hur olik…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>PE3002</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4964,24 +4964,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PE3003</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>30 ord: - är medveten om att han/hon är en myndighetsperson, dvs. kan hantera arbetsrela…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5018,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - kan visa hur han/hon arbetar aktivt i linje med högskolelagens/förordningens f…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>30 ord: - är medveten om att han/hon är en myndighetsperson, dvs. kan hantera arbetsrela…</t>
+          <t>41 ord: - kan analysera och diskutera studenters lärande i högre utbildning med hjälp av…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>27 ord: - kan visa hur han/hon arbetar aktivt i linje med högskolelagens/förordningens f…</t>
+          <t>26 ord: - kan påvisa yttringar av lärandet hos studenter och hos sig själv och koppla de…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>41 ord: - kan analysera och diskutera studenters lärande i högre utbildning med hjälp av…</t>
+          <t>36 ord: - inom det egna kunskapsområdet kan formulera mål och förväntade studieresultat,…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>26 ord: - kan påvisa yttringar av lärandet hos studenter och hos sig själv och koppla de…</t>
+          <t>32 ord: - kan beskriva, analysera och diskutera egna och andras erfarenheter genom jämfö…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>36 ord: - inom det egna kunskapsområdet kan formulera mål och förväntade studieresultat,…</t>
+          <t>28 ord: - kan planera och genomföra, redovisa och med kollegor diskutera ett självständi…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -5170,39 +5170,39 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>32 ord: - kan beskriva, analysera och diskutera egna och andras erfarenheter genom jämfö…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5212,51 +5212,51 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>28 ord: - kan planera och genomföra, redovisa och med kollegor diskutera ett självständi…</t>
+          <t>28 ord: - ange hur det valda temat förhåller sig till personalarbete i stort och hur det…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - med fördjupad kommunikationsförmåga både skriftligt och muntligt presentera, a…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>28 ord: - ange hur det valda temat förhåller sig till personalarbete i stort och hur det…</t>
+          <t>28 ord: - visa fördjupad kunskap om och använda sig av centrala vetenskapsteoretiska beg…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>26 ord: - med fördjupad kommunikationsförmåga både skriftligt och muntligt presentera, a…</t>
+          <t>29 ord: - visa kunskaper om olika modeller för och teorier om utvärdering och skolutveck…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad kunskap om och använda sig av centrala vetenskapsteoretiska beg…</t>
+          <t>33 ord: - visa förmåga att kritiskt och självständigt tillämpa och reflektera över relev…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om olika modeller för och teorier om utvärdering och skolutveck…</t>
+          <t>27 ord: - på egen hand och tillsammans med andra planera, genomföra, utvärdera och utvec…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att kritiskt och självständigt tillämpa och reflektera över relev…</t>
+          <t>34 ord: - visa fördjupad kunskap om och förmåga att systematiskt analysera och organiser…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>27 ord: - på egen hand och tillsammans med andra planera, genomföra, utvärdera och utvec…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>34 ord: - visa fördjupad kunskap om och förmåga att systematiskt analysera och organiser…</t>
+          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
+          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
+          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
+          <t>32 ord: - visa fördjupad förmåga att självständigt planera, genomföra, utvärdera och utv…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
+          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5590,19 +5590,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att självständigt planera, genomföra, utvärdera och utv…</t>
+          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
+          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
+          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
+          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
+          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
+          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
+          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
+          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
+          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5963,24 +5963,24 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
+          <t>29 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
@@ -6017,12 +6017,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>30 ord: - utifrån ämnesdidaktiska och specialpedagogiska överväganden och med ett kritis…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -6034,7 +6034,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6044,24 +6044,24 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6076,19 +6076,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>30 ord: - utifrån ämnesdidaktiska och specialpedagogiska överväganden och med ett kritis…</t>
+          <t>30 ord: - analysera vilka faktorer som främjar respektive försvårar olika professioners …</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6098,24 +6098,24 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - självständigt och tillsammans med andra organisera undervisning som förankras …</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6125,24 +6125,24 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>30 ord: - analysera vilka faktorer som främjar respektive försvårar olika professioners …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>27 ord: - självständigt och tillsammans med andra organisera undervisning som förankras …</t>
+          <t>26 ord: - visa förmåga att sammanhållet genomföra adekvat och etisk försvarbar dokumenta…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>32 ord: - kunna kritiskt värdera traditionsbaserad undervisningspraktik inom den egna in…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG2C6</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att sammanhållet genomföra adekvat och etisk försvarbar dokumenta…</t>
+          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG2C6</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6238,19 +6238,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>32 ord: - kunna kritiskt värdera traditionsbaserad undervisningspraktik inom den egna in…</t>
+          <t>30 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>APG2C6</t>
+          <t>APG2C7</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
+          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>APG2C6</t>
+          <t>APG2C7</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>30 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
+          <t>32 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
+          <t>26 ord: - föra professionella samtal på ett fördjupat sätt om planering, genomförande oc…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>32 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
+          <t>32 ord: - skriftligt och muntligt, utifrån de normer som finns för formell svenska och v…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>APG2CL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,19 +6373,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>26 ord: - föra professionella samtal på ett fördjupat sätt om planering, genomförande oc…</t>
+          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>APG2CL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6400,19 +6400,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>32 ord: - skriftligt och muntligt, utifrån de normer som finns för formell svenska och v…</t>
+          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>APG2CL</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6432,14 +6432,14 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>APG2CL</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6459,14 +6459,14 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6481,19 +6481,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
+          <t>33 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6508,19 +6508,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
+          <t>34 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6589,19 +6589,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>34 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
+          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
+          <t>33 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6665,24 +6665,24 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>33 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
+          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6746,24 +6746,24 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
+          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6827,24 +6827,24 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
+          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
@@ -6881,12 +6881,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
+          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
+          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
+          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6989,24 +6989,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
+          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
+          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
@@ -7043,12 +7043,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
+          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
+          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
+          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
+          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7178,24 +7178,24 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
+          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
+          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
+          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
+          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -7330,7 +7330,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7340,24 +7340,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
+          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
+          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
+          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
+          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
+          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
+          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7534,19 +7534,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>28 ord: - visa förmåga att utifrån kursens teorier analysera, problematisera och kommuni…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7561,19 +7561,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7583,24 +7583,24 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån kursens teorier analysera, problematisera och kommuni…</t>
+          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - visa kunskaper om mytens och andra berättelsers identitetsskapande funktion i …</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
+          <t>29 ord: - reflektera över hur digitala verktyg och digitala miljöer kan användas i under…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7691,24 +7691,24 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om mytens och andra berättelsers identitetsskapande funktion i …</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>29 ord: - reflektera över hur digitala verktyg och digitala miljöer kan användas i under…</t>
+          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
@@ -7745,12 +7745,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
+          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
+          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
+          <t>31 ord: - visa förmåga att självständigt planera, genomföra, utvärdera och utveckla unde…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
+          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7885,19 +7885,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att självständigt planera, genomföra, utvärdera och utveckla unde…</t>
+          <t>28 ord: - visa fördjupad förmåga att kritiskt och självständigt tillvarata och reflekter…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7912,19 +7912,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>34 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7939,19 +7939,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att kritiskt och självständigt tillvarata och reflekter…</t>
+          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
+          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -8032,7 +8032,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
+          <t>28 ord: - visa förmåga att, utifrån den egna undervisningen, analysera, värdera och komm…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>27 ord: - visa kunskap om olika teoretiska perspektiv på utveckling och lärande samt vis…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8101,19 +8101,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att, utifrån den egna undervisningen, analysera, värdera och komm…</t>
+          <t>27 ord: - visa förmåga att identifiera elevers behov av specialpedagogiska insatser, inb…</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika teoretiska perspektiv på utveckling och lärande samt vis…</t>
+          <t>28 ord: - visa förmåga att utifrån olika teorier analysera, problematisera och kommunice…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att identifiera elevers behov av specialpedagogiska insatser, inb…</t>
+          <t>39 ord: - visa förmåga att utifrån de teorier som behandlas i kursen och erfarenheter i …</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>GPG326</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån olika teorier analysera, problematisera och kommunice…</t>
+          <t>27 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>GPG327</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att utifrån de teorier som behandlas i kursen och erfarenheter i …</t>
+          <t>26 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GPG327</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
+          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
+          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
+          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
+          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
+          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
+          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG33D</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8452,19 +8452,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
+          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
+          <t>32 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GPG33D</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8528,24 +8528,24 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
+          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
+          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
+          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8663,24 +8663,24 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
+          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
+          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
+          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG3AE</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8803,19 +8803,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
+          <t>27 ord: - redogöra för olika teoretiska perspektiv på lärande, utveckling och kunskap sa…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG3AE</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8830,19 +8830,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
+          <t>31 ord: - diskutera olika digitala lärresursers möjligheter och begränsningar i den peda…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GPG3AE</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8857,19 +8857,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för olika teoretiska perspektiv på lärande, utveckling och kunskap sa…</t>
+          <t>30 ord: - i tal och skrift, argumentera för val av innehåll och arbetsformer i den egna …</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GPG3AE</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8884,19 +8884,19 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>31 ord: - diskutera olika digitala lärresursers möjligheter och begränsningar i den peda…</t>
+          <t>27 ord: - i den egna undervisningen, aktivt verka för skolans värdegrund och samhällsupp…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8906,24 +8906,24 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>30 ord: - i tal och skrift, argumentera för val av innehåll och arbetsformer i den egna …</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8938,19 +8938,19 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>27 ord: - i den egna undervisningen, aktivt verka för skolans värdegrund och samhällsupp…</t>
+          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8970,14 +8970,14 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8997,14 +8997,14 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9019,19 +9019,19 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9046,19 +9046,19 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
+          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9078,14 +9078,14 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9105,14 +9105,14 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9127,19 +9127,19 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
+          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
@@ -9176,12 +9176,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - med utgångspunkt i praktikens didaktiska villkor och utifrån ett hållbarhetspe…</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -9193,7 +9193,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9203,24 +9203,24 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>27 ord: - med utgångspunkt i praktikens didaktiska villkor och utifrån ett hållbarhetspe…</t>
+          <t>27 ord: - identifiera och beakta grundläggande demokratiska värderingar samt olika jämst…</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9262,19 +9262,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9284,24 +9284,24 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och beakta grundläggande demokratiska värderingar samt olika jämst…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 0 hp)</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9311,24 +9311,24 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9338,24 +9338,24 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 0 hp)</t>
+          <t>38 ord: - identifiera och diskutera problem samt föreslå utvecklingsområden i den pedago…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9370,19 +9370,19 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>27 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
+          <t>28 ord: - utifrån egna erfarenheter i den pedagogiska verksamheten och tidigare forsknin…</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9397,19 +9397,19 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>38 ord: - identifiera och diskutera problem samt föreslå utvecklingsområden i den pedago…</t>
+          <t>34 ord: - använda det engelska språket för att i samarbete i internationellt blandade gr…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9424,19 +9424,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån egna erfarenheter i den pedagogiska verksamheten och tidigare forsknin…</t>
+          <t>29 ord: - kritiskt reflektera över sin egen interkulturella kompetens och det interkultu…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>34 ord: - använda det engelska språket för att i samarbete i internationellt blandade gr…</t>
+          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9478,19 +9478,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>29 ord: - kritiskt reflektera över sin egen interkulturella kompetens och det interkultu…</t>
+          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
+          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -9532,24 +9532,24 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
+          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -9559,19 +9559,19 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
+          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
+          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9613,19 +9613,19 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
+          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9635,24 +9635,24 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9667,19 +9667,19 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9699,14 +9699,14 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
@@ -9743,12 +9743,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -9787,61 +9787,61 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9851,24 +9851,24 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9888,14 +9888,14 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9915,14 +9915,14 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9942,14 +9942,14 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9964,19 +9964,19 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9986,24 +9986,24 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10013,24 +10013,24 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10040,24 +10040,24 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10067,24 +10067,24 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10094,24 +10094,24 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10121,24 +10121,24 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10148,24 +10148,24 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10175,29 +10175,29 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10207,24 +10207,24 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10234,24 +10234,24 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10261,19 +10261,19 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10293,14 +10293,14 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10320,14 +10320,14 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10347,14 +10347,14 @@
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10364,24 +10364,24 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10396,19 +10396,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10423,19 +10423,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10445,24 +10445,24 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10477,19 +10477,19 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10504,19 +10504,19 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
+          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10531,19 +10531,19 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
+          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10563,14 +10563,14 @@
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10585,19 +10585,19 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
+          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10612,100 +10612,100 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10720,19 +10720,19 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10747,19 +10747,19 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10774,19 +10774,19 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10801,100 +10801,100 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>ATR2BB</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>ATR2BB</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10904,24 +10904,24 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10931,24 +10931,24 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10958,24 +10958,24 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10985,24 +10985,24 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -11012,24 +11012,24 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR3010</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11039,105 +11039,105 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -11147,24 +11147,24 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -11179,19 +11179,19 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -11206,19 +11206,19 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -11233,19 +11233,19 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
+          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -11260,19 +11260,19 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -11282,24 +11282,24 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11314,19 +11314,19 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
+          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11336,24 +11336,24 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11368,19 +11368,19 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
+          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -11395,19 +11395,19 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11422,19 +11422,19 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
+          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11449,19 +11449,19 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
+          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>AS3011</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11471,24 +11471,24 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11498,24 +11498,24 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>AS4004</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11530,19 +11530,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
+          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>AS4004</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11552,24 +11552,24 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
+          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>AS4004</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11579,103 +11579,22 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
+          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="2" t="inlineStr">
-        <is>
-          <t>AS4004</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
-        </is>
-      </c>
-      <c r="E414" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" s="2" t="inlineStr">
-        <is>
-          <t>AS4004</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
-        </is>
-      </c>
-      <c r="E415" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="2" t="inlineStr">
-        <is>
-          <t>AS4004</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
-        </is>
-      </c>
-      <c r="E416" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E416"/>
+  <autoFilter ref="A1:E413"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -12501,12 +12420,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E412" r:id="rId822"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A413" r:id="rId823"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E413" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A414" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E414" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A415" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E415" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A416" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E416" r:id="rId830"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$412</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E413"/>
+  <dimension ref="A1:E412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4630,7 +4630,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PE1053</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4640,24 +4640,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 5 hp)</t>
+          <t>37 ord: - använda pedagogisk dokumentation som underlag för att tillsammans med kollegor…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>PE1055</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>37 ord: - använda pedagogisk dokumentation som underlag för att tillsammans med kollegor…</t>
+          <t>38 ord: - beskriva, dokumentera och analysera möjligheter och hinder i förskolans verksa…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PE1055</t>
+          <t>PE1056</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva, dokumentera och analysera möjligheter och hinder i förskolans verksa…</t>
+          <t>26 ord: - identifiera och reflektera över vad det innebär att planera, följa upp, utvärd…</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>26 ord: - identifiera och reflektera över vad det innebär att planera, följa upp, utvärd…</t>
+          <t>26 ord: - beskriva och analysera hur förskolechefen kan planera och leda arbetsprocesser…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PE1056</t>
+          <t>PE1062</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4748,24 +4748,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>26 ord: - beskriva och analysera hur förskolechefen kan planera och leda arbetsprocesser…</t>
+          <t>5 lärandemål (maximum rekommenderat: 4 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1062</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PE1060</t>
+          <t>PE1070</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4775,24 +4775,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>26 ord: - visa kunskap om vilka steg som bör tas för att bygga upp organisationen i form…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PE1070</t>
+          <t>PE1072</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4802,17 +4802,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om vilka steg som bör tas för att bygga upp organisationen i form…</t>
+          <t>5 lärandemål (maximum rekommenderat: 4 för 1.5 hp)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1072</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 0 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 1 för 0 hp)</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 1.5 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9851,17 +9851,17 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
@@ -9878,12 +9878,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9905,24 +9905,24 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9932,17 +9932,17 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
+          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9986,24 +9986,24 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10018,19 +10018,19 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10045,19 +10045,19 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10067,24 +10067,24 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10094,24 +10094,24 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10126,19 +10126,19 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
+          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10153,24 +10153,24 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
+          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10180,19 +10180,19 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10261,19 +10261,19 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10337,24 +10337,24 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10364,17 +10364,17 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
+          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10423,19 +10423,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
+          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10450,19 +10450,19 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
+          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10531,19 +10531,19 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10558,19 +10558,19 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10585,46 +10585,46 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10639,19 +10639,19 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10666,19 +10666,19 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10693,19 +10693,19 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10725,14 +10725,14 @@
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10747,19 +10747,19 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10774,46 +10774,46 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>ATR2BB</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>ATR2BB</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10828,19 +10828,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
+          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10855,19 +10855,19 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
+          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10877,24 +10877,24 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10914,14 +10914,14 @@
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10931,24 +10931,24 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10958,24 +10958,24 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10985,24 +10985,24 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>TR3010</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -11012,51 +11012,51 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11071,19 +11071,19 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -11137,7 +11137,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -11147,24 +11147,24 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -11179,12 +11179,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
@@ -11201,12 +11201,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
@@ -11255,12 +11255,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
+          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
+          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
+          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
+          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -11407,7 +11407,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11422,19 +11422,19 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
+          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>AS3011</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11444,24 +11444,24 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11476,19 +11476,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>AS4004</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11498,17 +11498,17 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
+          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
+          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -11566,35 +11566,8 @@
         </is>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" s="2" t="inlineStr">
-        <is>
-          <t>AS4004</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
-        </is>
-      </c>
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E413"/>
+  <autoFilter ref="A1:E412"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -12418,8 +12391,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E411" r:id="rId820"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A412" r:id="rId821"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E412" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A413" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E413" r:id="rId824"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$434</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E412"/>
+  <dimension ref="A1:E434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5170,66 +5170,66 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>FPA0001</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>28 ord: - ange hur det valda temat förhåller sig till personalarbete i stort och hur det…</t>
+          <t>0 lärandemål (minimum rekommenderat: 2 för 4.5 hp)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5239,24 +5239,24 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>26 ord: - med fördjupad kommunikationsförmåga både skriftligt och muntligt presentera, a…</t>
+          <t>26 ord: - kunna redogöra för och diskutera värdegrundsuppdraget och mänskliga rättighete…</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5266,24 +5266,24 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad kunskap om och använda sig av centrala vetenskapsteoretiska beg…</t>
+          <t>35 ord: - kunna problematisera en komplex skolpraktik utifrån några centrala begreppslig…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5293,24 +5293,24 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om olika modeller för och teorier om utvärdering och skolutveck…</t>
+          <t>32 ord: - kunna värdera och kritiskt förhålla sig till värdegrundsuppdraget i skolan, ge…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att kritiskt och självständigt tillämpa och reflektera över relev…</t>
+          <t>31 ord: - visa en förmåga att ta ansvar för sin kunskapsutveckling genom att reflektera …</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5347,24 +5347,24 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>27 ord: - på egen hand och tillsammans med andra planera, genomföra, utvärdera och utvec…</t>
+          <t>27 ord: - visa fördjupad förståelse för betydelsen av teoretisk förankring i relation ti…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5374,51 +5374,51 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>34 ord: - visa fördjupad kunskap om och förmåga att systematiskt analysera och organiser…</t>
+          <t>31 ord: - identifiera, problematisera och värdera olika typer av kunskapsbidrag inom ram…</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>37 ord: - visa kunskap och förtrogenhet med praktiknära forskning genom att redogöra för…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5428,105 +5428,105 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
+          <t>29 ord: - visa förmåga till kritiskt, reflekterande och självständigt tänkande genom att…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
+          <t>0 lärandemål (minimum rekommenderat: 1 för 3 hp)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5536,267 +5536,267 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att självständigt planera, genomföra, utvärdera och utv…</t>
+          <t>29 ord: - visa förmåga till kritiskt, reflekterande och självständigt tänkande i relatio…</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 10 hp)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
+          <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 6 hp)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
+          <t>0 lärandemål (minimum rekommenderat: 2 för 4 hp)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 10 hp)</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
+          <t>28 ord: - ange hur det valda temat förhåller sig till personalarbete i stort och hur det…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
+          <t>26 ord: - med fördjupad kommunikationsförmåga både skriftligt och muntligt presentera, a…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5860,19 +5860,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>28 ord: - visa fördjupad kunskap om och använda sig av centrala vetenskapsteoretiska beg…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5887,19 +5887,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
+          <t>29 ord: - visa kunskaper om olika modeller för och teorier om utvärdering och skolutveck…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
+          <t>33 ord: - visa förmåga att kritiskt och självständigt tillämpa och reflektera över relev…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5941,19 +5941,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
+          <t>27 ord: - på egen hand och tillsammans med andra planera, genomföra, utvärdera och utvec…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5963,24 +5963,24 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>34 ord: - visa fördjupad kunskap om och förmåga att systematiskt analysera och organiser…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5990,24 +5990,24 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6022,19 +6022,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>30 ord: - utifrån ämnesdidaktiska och specialpedagogiska överväganden och med ett kritis…</t>
+          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6044,24 +6044,24 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6076,19 +6076,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>30 ord: - analysera vilka faktorer som främjar respektive försvårar olika professioners …</t>
+          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6103,19 +6103,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>27 ord: - självständigt och tillsammans med andra organisera undervisning som förankras …</t>
+          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6125,24 +6125,24 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>32 ord: - visa fördjupad förmåga att självständigt planera, genomföra, utvärdera och utv…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6157,19 +6157,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att sammanhållet genomföra adekvat och etisk försvarbar dokumenta…</t>
+          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6184,19 +6184,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>32 ord: - kunna kritiskt värdera traditionsbaserad undervisningspraktik inom den egna in…</t>
+          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>APG2C6</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
+          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>APG2C6</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6238,19 +6238,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>30 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
+          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
+          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>32 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
+          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>26 ord: - föra professionella samtal på ett fördjupat sätt om planering, genomförande oc…</t>
+          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>32 ord: - skriftligt och muntligt, utifrån de normer som finns för formell svenska och v…</t>
+          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>APG2CL</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,19 +6373,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
+          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>APG2CL</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6400,19 +6400,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
+          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6427,19 +6427,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
+          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6454,19 +6454,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
+          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6481,19 +6481,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6508,19 +6508,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
+          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6535,19 +6535,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6557,24 +6557,24 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>34 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6589,19 +6589,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
+          <t>29 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>30 ord: - utifrån ämnesdidaktiska och specialpedagogiska överväganden och med ett kritis…</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6638,24 +6638,24 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>33 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6665,24 +6665,24 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - analysera vilka faktorer som främjar respektive försvårar olika professioners …</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6697,19 +6697,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
+          <t>27 ord: - självständigt och tillsammans med andra organisera undervisning som förankras …</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6719,24 +6719,24 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6746,24 +6746,24 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - visa förmåga att sammanhållet genomföra adekvat och etisk försvarbar dokumenta…</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
+          <t>32 ord: - kunna kritiskt värdera traditionsbaserad undervisningspraktik inom den egna in…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>APG2C6</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
+          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG2C6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6827,24 +6827,24 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG2C7</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6859,19 +6859,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
+          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG2C7</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6886,19 +6886,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
+          <t>32 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
+          <t>26 ord: - föra professionella samtal på ett fördjupat sätt om planering, genomförande oc…</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6940,19 +6940,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
+          <t>32 ord: - skriftligt och muntligt, utifrån de normer som finns för formell svenska och v…</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG2CL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
+          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>APG2CL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6989,24 +6989,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
+          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
+          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
+          <t>33 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7102,19 +7102,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7129,19 +7129,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
+          <t>34 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7178,24 +7178,24 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
+          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
+          <t>33 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7259,24 +7259,24 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7291,19 +7291,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
+          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7318,19 +7318,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
+          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7345,19 +7345,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7372,19 +7372,19 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
+          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7399,19 +7399,19 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
+          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7421,24 +7421,24 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7453,19 +7453,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
+          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7480,19 +7480,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7507,19 +7507,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
+          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7534,19 +7534,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån kursens teorier analysera, problematisera och kommuni…</t>
+          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7561,19 +7561,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7588,19 +7588,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7615,19 +7615,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
+          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7642,19 +7642,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om mytens och andra berättelsers identitetsskapande funktion i …</t>
+          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7669,19 +7669,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>29 ord: - reflektera över hur digitala verktyg och digitala miljöer kan användas i under…</t>
+          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7691,24 +7691,24 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7723,19 +7723,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
+          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7750,19 +7750,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
+          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7772,24 +7772,24 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
+          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7831,19 +7831,19 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att självständigt planera, genomföra, utvärdera och utveckla unde…</t>
+          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7858,19 +7858,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7885,19 +7885,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att kritiskt och självständigt tillvarata och reflekter…</t>
+          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7912,19 +7912,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7934,24 +7934,24 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
+          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7966,19 +7966,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7993,19 +7993,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
+          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att, utifrån den egna undervisningen, analysera, värdera och komm…</t>
+          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika teoretiska perspektiv på utveckling och lärande samt vis…</t>
+          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8101,19 +8101,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att identifiera elevers behov av specialpedagogiska insatser, inb…</t>
+          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån olika teorier analysera, problematisera och kommunice…</t>
+          <t>28 ord: - visa förmåga att utifrån kursens teorier analysera, problematisera och kommuni…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att utifrån de teorier som behandlas i kursen och erfarenheter i …</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8177,24 +8177,24 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GPG327</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
+          <t>27 ord: - visa kunskaper om mytens och andra berättelsers identitetsskapande funktion i …</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
+          <t>29 ord: - reflektera över hur digitala verktyg och digitala miljöer kan användas i under…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8285,24 +8285,24 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
+          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
+          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
+          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
+          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8425,19 +8425,19 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
+          <t>31 ord: - visa förmåga att självständigt planera, genomföra, utvärdera och utveckla unde…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GPG33D</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8452,19 +8452,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
+          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>28 ord: - visa fördjupad förmåga att kritiskt och självständigt tillvarata och reflekter…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,19 +8506,19 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
+          <t>34 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8528,24 +8528,24 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8560,19 +8560,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
+          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8587,19 +8587,19 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
+          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8614,19 +8614,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
+          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8641,19 +8641,19 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
+          <t>28 ord: - visa förmåga att, utifrån den egna undervisningen, analysera, värdera och komm…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8663,24 +8663,24 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - visa kunskap om olika teoretiska perspektiv på utveckling och lärande samt vis…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8695,19 +8695,19 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
+          <t>27 ord: - visa förmåga att identifiera elevers behov av specialpedagogiska insatser, inb…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8722,19 +8722,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
+          <t>28 ord: - visa förmåga att utifrån olika teorier analysera, problematisera och kommunice…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8749,19 +8749,19 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
+          <t>39 ord: - visa förmåga att utifrån de teorier som behandlas i kursen och erfarenheter i …</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG326</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8776,19 +8776,19 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
+          <t>27 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GPG3AE</t>
+          <t>GPG327</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8803,19 +8803,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för olika teoretiska perspektiv på lärande, utveckling och kunskap sa…</t>
+          <t>26 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GPG3AE</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8830,19 +8830,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>31 ord: - diskutera olika digitala lärresursers möjligheter och begränsningar i den peda…</t>
+          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8857,19 +8857,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>30 ord: - i tal och skrift, argumentera för val av innehåll och arbetsformer i den egna …</t>
+          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8884,19 +8884,19 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>27 ord: - i den egna undervisningen, aktivt verka för skolans värdegrund och samhällsupp…</t>
+          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8906,24 +8906,24 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8938,19 +8938,19 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
+          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8960,24 +8960,24 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
+          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9014,24 +9014,24 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG33D</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9046,19 +9046,19 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
+          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9068,24 +9068,24 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9100,19 +9100,19 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
+          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9127,19 +9127,19 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9154,19 +9154,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
+          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9181,19 +9181,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>27 ord: - med utgångspunkt i praktikens didaktiska villkor och utifrån ett hållbarhetspe…</t>
+          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9203,24 +9203,24 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och beakta grundläggande demokratiska värderingar samt olika jämst…</t>
+          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9262,19 +9262,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9284,24 +9284,24 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 1 för 0 hp)</t>
+          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9316,19 +9316,19 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>27 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
+          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9343,19 +9343,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>38 ord: - identifiera och diskutera problem samt föreslå utvecklingsområden i den pedago…</t>
+          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9370,19 +9370,19 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån egna erfarenheter i den pedagogiska verksamheten och tidigare forsknin…</t>
+          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>GPG3AE</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9397,19 +9397,19 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>34 ord: - använda det engelska språket för att i samarbete i internationellt blandade gr…</t>
+          <t>27 ord: - redogöra för olika teoretiska perspektiv på lärande, utveckling och kunskap sa…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>GPG3AE</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9424,19 +9424,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>29 ord: - kritiskt reflektera över sin egen interkulturella kompetens och det interkultu…</t>
+          <t>31 ord: - diskutera olika digitala lärresursers möjligheter och begränsningar i den peda…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
+          <t>30 ord: - i tal och skrift, argumentera för val av innehåll och arbetsformer i den egna …</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9478,19 +9478,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
+          <t>27 ord: - i den egna undervisningen, aktivt verka för skolans värdegrund och samhällsupp…</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9500,29 +9500,29 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -9532,51 +9532,51 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
+          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9586,159 +9586,159 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
+          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
+          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -9748,24 +9748,24 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -9775,51 +9775,51 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>27 ord: - med utgångspunkt i praktikens didaktiska villkor och utifrån ett hållbarhetspe…</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -9829,105 +9829,105 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>27 ord: - identifiera och beakta grundläggande demokratiska värderingar samt olika jämst…</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>0 lärandemål (minimum rekommenderat: 1 för 0 hp)</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>27 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
+          <t>38 ord: - identifiera och diskutera problem samt föreslå utvecklingsområden i den pedago…</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9964,132 +9964,132 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
+          <t>28 ord: - utifrån egna erfarenheter i den pedagogiska verksamheten och tidigare forsknin…</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>34 ord: - använda det engelska språket för att i samarbete i internationellt blandade gr…</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>29 ord: - kritiskt reflektera över sin egen interkulturella kompetens och det interkultu…</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
+          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10126,24 +10126,24 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
+          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10153,24 +10153,24 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
+          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10180,24 +10180,24 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10207,51 +10207,51 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10261,51 +10261,51 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10315,51 +10315,51 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10369,51 +10369,51 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -10423,51 +10423,51 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10477,51 +10477,51 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -10531,24 +10531,24 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10558,105 +10558,105 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
+          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10666,132 +10666,132 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>ATR2BB</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10801,24 +10801,24 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10828,24 +10828,24 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10855,105 +10855,105 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10963,51 +10963,51 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
+          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11017,105 +11017,105 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
+          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11125,267 +11125,267 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>ATR2BB</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -11395,24 +11395,24 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
+          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -11422,51 +11422,51 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
+          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
+          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -11476,98 +11476,692 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>AS4004</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>AS4004</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
+          <t>TR1016</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>TR3010</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>AS2001</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>AS2003</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>AS2003</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>AS3001</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>AS3006</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>AS3006</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>AS3011</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
           <t>AS4004</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B432" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>AS4004</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>AS4004</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
         <is>
           <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
-      <c r="E412" s="2" t="inlineStr">
+      <c r="E434" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E412"/>
+  <autoFilter ref="A1:E434"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -12391,6 +12985,50 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E411" r:id="rId820"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A412" r:id="rId821"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E412" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A413" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E413" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A414" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E414" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A415" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E415" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A416" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E416" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A417" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E417" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A418" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E418" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A419" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E419" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A420" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E420" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A421" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E421" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A422" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E422" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A423" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E423" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A424" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E424" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A425" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E425" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A426" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E426" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A427" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E427" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A428" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E428" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A429" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E429" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A430" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E430" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A431" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E431" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A432" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E432" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A433" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E433" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A434" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E434" r:id="rId866"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$434</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$436</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10030,7 +10030,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG3KA</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10045,19 +10045,19 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
+          <t>28 ord: - diskutera och analysera den egna undervisningen, samt i samarbete med verksamm…</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KA</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GPG3KB</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10072,19 +10072,19 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
+          <t>28 ord: - diskutera och analysera den egna undervisningen, samt i samarbete med verksamm…</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
+          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10126,24 +10126,24 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
+          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10153,19 +10153,19 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
+          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10180,19 +10180,19 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
+          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10207,19 +10207,19 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10229,24 +10229,24 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10261,19 +10261,19 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10293,14 +10293,14 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
@@ -10337,12 +10337,12 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -10381,39 +10381,39 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -10423,19 +10423,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10455,14 +10455,14 @@
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10482,14 +10482,14 @@
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10509,14 +10509,14 @@
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10531,19 +10531,19 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10553,24 +10553,24 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10580,24 +10580,24 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10607,24 +10607,24 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10644,14 +10644,14 @@
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10661,24 +10661,24 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10688,24 +10688,24 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10715,24 +10715,24 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10747,24 +10747,24 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
+          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10774,24 +10774,24 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10801,19 +10801,19 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10828,19 +10828,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10855,19 +10855,19 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10882,19 +10882,19 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10909,19 +10909,19 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10931,24 +10931,24 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10963,19 +10963,19 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10985,24 +10985,24 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -11017,19 +11017,19 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
+          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11044,19 +11044,19 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11071,19 +11071,19 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
+          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11098,19 +11098,19 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -11125,19 +11125,19 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -11152,19 +11152,19 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
+          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -11179,73 +11179,73 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -11260,19 +11260,19 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -11287,19 +11287,19 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11314,19 +11314,19 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11341,19 +11341,19 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11368,73 +11368,73 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>ATR2BB</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>ATR2BB</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11449,19 +11449,19 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
+          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11471,24 +11471,24 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11498,24 +11498,24 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11525,24 +11525,24 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11552,24 +11552,24 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11584,19 +11584,19 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -11611,73 +11611,73 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
+          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>TR3010</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -11692,19 +11692,19 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -11714,24 +11714,24 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -11746,19 +11746,19 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -11768,24 +11768,24 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -11795,24 +11795,24 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -11827,19 +11827,19 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -11854,19 +11854,19 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
+          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -11876,24 +11876,24 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
+          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
+          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -11947,7 +11947,7 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11962,19 +11962,19 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
+          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11989,19 +11989,19 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
+          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -12016,19 +12016,19 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
+          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -12038,24 +12038,24 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
+          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -12065,24 +12065,24 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
+          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>AS4004</t>
+          <t>AS3011</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -12092,24 +12092,24 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>AS4004</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -12119,17 +12119,17 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
@@ -12151,17 +12151,71 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
+          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>AS4004</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>AS4004</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
           <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
-      <c r="E434" s="2" t="inlineStr">
+      <c r="E436" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E434"/>
+  <autoFilter ref="A1:E436"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -13029,6 +13083,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E433" r:id="rId864"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A434" r:id="rId865"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E434" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A435" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E435" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A436" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E436" r:id="rId870"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$436</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$437</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G436"/>
+  <dimension ref="A1:G437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7418,7 +7418,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2020-04-23</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -7439,19 +7439,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>27 ord: - på egen hand och tillsammans med andra planera, genomföra, utvärdera och utvec…</t>
+          <t>27 ord: - med stöd av olika verksamhetsnära metodansatser skriftligt och muntligt analys…</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -7472,19 +7472,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>34 ord: - visa fördjupad kunskap om och förmåga att systematiskt analysera och organiser…</t>
+          <t>27 ord: - på egen hand och tillsammans med andra planera, genomföra, utvärdera och utvec…</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7494,23 +7494,23 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>34 ord: - visa fördjupad kunskap om och förmåga att systematiskt analysera och organiser…</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
@@ -7533,12 +7533,12 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
+          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
+          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
+          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att självständigt planera, genomföra, utvärdera och utv…</t>
+          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>32 ord: - visa fördjupad förmåga att självständigt planera, genomföra, utvärdera och utv…</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -7715,7 +7715,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -7736,12 +7736,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
+          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
+          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -7868,12 +7868,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
+          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
+          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
+          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
+          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
+          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>27 ord: - visa fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs för den egna un…</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
+          <t>36 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
+          <t>27 ord: - visa förmåga att, med utgångspunkt i forskning och erfarenhetsbaserad kunskap,…</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
+          <t>35 ord: - visa förmåga att observera, dokumentera, analysera, och i samarbete med verksa…</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -8177,7 +8177,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8187,23 +8187,23 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>33 ord: - visa förmåga att, med ett kritiskt förhållningssätt utifrån ämnesdidaktiska öv…</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>30 ord: - utifrån ämnesdidaktiska och specialpedagogiska överväganden och med ett kritis…</t>
+          <t>29 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -8276,7 +8276,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8286,30 +8286,30 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - utifrån ämnesdidaktiska och specialpedagogiska överväganden och med ett kritis…</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8319,30 +8319,30 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>30 ord: - analysera vilka faktorer som främjar respektive försvårar olika professioners …</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -8363,19 +8363,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>27 ord: - självständigt och tillsammans med andra organisera undervisning som förankras …</t>
+          <t>30 ord: - analysera vilka faktorer som främjar respektive försvårar olika professioners …</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8385,23 +8385,23 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - självständigt och tillsammans med andra organisera undervisning som förankras …</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
@@ -8424,12 +8424,12 @@
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att sammanhållet genomföra adekvat och etisk försvarbar dokumenta…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>32 ord: - kunna kritiskt värdera traditionsbaserad undervisningspraktik inom den egna in…</t>
+          <t>26 ord: - visa förmåga att sammanhållet genomföra adekvat och etisk försvarbar dokumenta…</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>APG2C6</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
+          <t>32 ord: - kunna kritiskt värdera traditionsbaserad undervisningspraktik inom den egna in…</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>30 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
+          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>APG2C6</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
+          <t>30 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>32 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
+          <t>27 ord: - utifrån relevanta teorier analysera och problematisera bedömningspraktiker i å…</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>APG2C7</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -8627,12 +8627,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>26 ord: - föra professionella samtal på ett fördjupat sätt om planering, genomförande oc…</t>
+          <t>32 ord: - identifiera, jämföra och problematisera olika metoder för att dokumentera och …</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>32 ord: - skriftligt och muntligt, utifrån de normer som finns för formell svenska och v…</t>
+          <t>26 ord: - föra professionella samtal på ett fördjupat sätt om planering, genomförande oc…</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>APG2CL</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
+          <t>32 ord: - skriftligt och muntligt, utifrån de normer som finns för formell svenska och v…</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
+          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>APG2CL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
+          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
+          <t>34 ord: - utifrån en nyanserad kunskap om de övergripande ramverken kritiskt reflektera …</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8814,14 +8814,10 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2018-03-08</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -8829,19 +8825,19 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>29 ord: - analysera och värdera egen och andras undervisnings genomförande och föreslå m…</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8851,10 +8847,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>2018-03-08</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
+          <t>33 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>34 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
+          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
+          <t>34 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier analysera, problematisera och kom…</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>33 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
+          <t>31 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9049,23 +9049,23 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>33 ord: - självständigt och i samarbete med verksamma lärare omsätta kunskaper inom ämne…</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
@@ -9088,12 +9088,12 @@
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
+          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9148,23 +9148,23 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
@@ -9187,12 +9187,12 @@
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
+          <t>32 ord: - visa förmåga att utifrån skolans styrdokument, teorier om motivation och språk…</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9247,23 +9247,23 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - visa förmåga att självständigt och kritiskt reflektera över den egna och andra…</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
+          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
+          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
+          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
+          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -9451,17 +9451,17 @@
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
+          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
+          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
+          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
+          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
+          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -9666,7 +9666,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9676,23 +9676,23 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2021-11-24</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
@@ -9715,12 +9715,12 @@
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
+          <t>35 ord: - visa kunskap om olika teorier om kunskap, lärande och utveckling för unga och …</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
+          <t>32 ord: - visa förmåga att identifiera sitt behov av fortsatt utveckling av det egna lär…</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
+          <t>27 ord: - visa kunskap om och förmåga att använda sig av centrala vetenskapsteoretiska b…</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
+          <t>27 ord: - visa kunskap om kvalitativa och kvantitativa forskningsmetoder och forskningst…</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9880,17 +9880,17 @@
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa förmåga att urskilja, analysera och värdera elevers skilda nivåer av ämne…</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
+          <t>16 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
+          <t>31 ord: - visa kunskap om olika orsaker till elevers behov av specialpedagogiska insatse…</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
+          <t>28 ord: - visa grundläggande kunskap om olika teoretiska perspektiv på specialpedagogik …</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
+          <t>27 ord: - visa kunskap om undervisning, lärande och bedömning inom ett ämnesdidaktiskt a…</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>39 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra oc…</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
+          <t>36 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GPG2S9</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån kursens teorier analysera, problematisera och kommuni…</t>
+          <t>31 ord: - visa förmåga till etiskt och medvetet förhållningssätt vid muntlig och skriftl…</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
+          <t>28 ord: - visa förmåga att utifrån kursens teorier analysera, problematisera och kommuni…</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2S9</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10177,17 +10177,17 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - visa förmåga att utifrån ovanstående teorier och erfarenheter i den egna under…</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S9</t>
         </is>
       </c>
     </row>
@@ -10210,12 +10210,12 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om mytens och andra berättelsers identitetsskapande funktion i …</t>
+          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>29 ord: - reflektera över hur digitala verktyg och digitala miljöer kan användas i under…</t>
+          <t>27 ord: - visa kunskaper om mytens och andra berättelsers identitetsskapande funktion i …</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -10293,7 +10293,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -10303,23 +10303,23 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - reflektera över hur digitala verktyg och digitala miljöer kan användas i under…</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
@@ -10342,12 +10342,12 @@
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
+          <t>30 ord: - visa kunskap om olika modeller för och teorier om utvärdering och skolutveckli…</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
+          <t>28 ord: - visa kunskap om utbildning för hållbar utveckling och professionellt lärarskap…</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
+          <t>34 ord: - visa förmåga att formulera ett bidrag till en hållbar utveckling av lärarprofe…</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att självständigt planera, genomföra, utvärdera och utveckla unde…</t>
+          <t>29 ord: - visa förmåga att möta eleverna i det egna undervisningsämnet genom att utgå fr…</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>31 ord: - visa förmåga att självständigt planera, genomföra, utvärdera och utveckla unde…</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -10545,19 +10545,19 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att kritiskt och självständigt tillvarata och reflekter…</t>
+          <t>27 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -10578,19 +10578,19 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>28 ord: - visa fördjupad förmåga att kritiskt och självständigt tillvarata och reflekter…</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -10611,12 +10611,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
+          <t>34 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
+          <t>28 ord: - visa förmåga att möta eleverna i den egna undervisningen genom att utgå från e…</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
+          <t>32 ord: - visa förmåga att självständigt och tillsammans med andra planera, genomföra, u…</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
+          <t>32 ord: - visa förmåga att med ett kritiskt förhållningssätt utifrån ämnesdidaktiska och…</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -10743,19 +10743,19 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att, utifrån den egna undervisningen, analysera, värdera och komm…</t>
+          <t>26 ord: - visa förmåga att självständigt och kritiskt analysera, diskutera och reflekter…</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika teoretiska perspektiv på utveckling och lärande samt vis…</t>
+          <t>28 ord: - visa förmåga att, utifrån den egna undervisningen, analysera, värdera och komm…</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att identifiera elevers behov av specialpedagogiska insatser, inb…</t>
+          <t>27 ord: - visa kunskap om olika teoretiska perspektiv på utveckling och lärande samt vis…</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att utifrån olika teorier analysera, problematisera och kommunice…</t>
+          <t>27 ord: - visa förmåga att identifiera elevers behov av specialpedagogiska insatser, inb…</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>39 ord: - visa förmåga att utifrån de teorier som behandlas i kursen och erfarenheter i …</t>
+          <t>28 ord: - visa förmåga att utifrån olika teorier analysera, problematisera och kommunice…</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
@@ -10887,7 +10887,7 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -10908,19 +10908,19 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>39 ord: - visa förmåga att utifrån de teorier som behandlas i kursen och erfarenheter i …</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GPG327</t>
+          <t>GPG326</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10941,19 +10941,19 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>27 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG327</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
+          <t>26 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
+          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
+          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
+          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -11106,12 +11106,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
+          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
+          <t>30 ord: - visa kunskaper om olika didaktiska och teoretiska perspektiv på lärande, utvec…</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
+          <t>29 ord: - visa kunskaper om och förmåga att aktivt verka för skolans värdegrund och samh…</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
+          <t>35 ord: - visa förmåga att, såväl i tal som i skrift, argumentera för val av innehåll oc…</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GPG33D</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -11238,19 +11238,19 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
+          <t>30 ord: - visa förmåga att självständigt och i samarbete med verksamma lärare planera, g…</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG33D</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
+          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
+          <t>32 ord: - visa förmåga att, utifrån skolans styrdokument, självständigt och i samarbete …</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
@@ -11316,7 +11316,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -11326,23 +11326,23 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - visa förmåga att tala och skriva i enlighet med normer för akademiskt språk oc…</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
@@ -11365,12 +11365,12 @@
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
+          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
+          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
+          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
+          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -11497,17 +11497,17 @@
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
@@ -11530,12 +11530,12 @@
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
+          <t>18 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
+          <t>27 ord: - visa förmåga att läsa, sammanfatta och referera innehåll i texter som är relev…</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
+          <t>27 ord: - visa förmåga att utifrån gällande skollag och läroplan för aktuell skolform kr…</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
+          <t>32 ord: - visa kunskap om sociala relationer och makt, genom att med hjälp av aktuell fo…</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
@@ -11646,7 +11646,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GPG3AE</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -11667,12 +11667,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för olika teoretiska perspektiv på lärande, utveckling och kunskap sa…</t>
+          <t>34 ord: - visa förmåga att reflektera över former för lärare att hantera, förebygga och …</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>31 ord: - diskutera olika digitala lärresursers möjligheter och begränsningar i den peda…</t>
+          <t>27 ord: - redogöra för olika teoretiska perspektiv på lärande, utveckling och kunskap sa…</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>GPG3AG</t>
+          <t>GPG3AE</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>30 ord: - i tal och skrift, argumentera för val av innehåll och arbetsformer i den egna …</t>
+          <t>31 ord: - diskutera olika digitala lärresursers möjligheter och begränsningar i den peda…</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AE</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>27 ord: - i den egna undervisningen, aktivt verka för skolans värdegrund och samhällsupp…</t>
+          <t>30 ord: - i tal och skrift, argumentera för val av innehåll och arbetsformer i den egna …</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG3AG</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11788,23 +11788,23 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - i den egna undervisningen, aktivt verka för skolans värdegrund och samhällsupp…</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AG</t>
         </is>
       </c>
     </row>
@@ -11827,12 +11827,12 @@
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G337" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -11860,17 +11860,17 @@
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
@@ -11893,12 +11893,12 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
@@ -11910,7 +11910,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -11926,17 +11926,17 @@
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - argumentera, vetenskapligt i tal och skrift, för val av innehåll och arbetsfor…</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
@@ -11959,12 +11959,12 @@
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G341" s="2" t="inlineStr">
@@ -11976,7 +11976,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -11992,17 +11992,17 @@
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
@@ -12025,12 +12025,12 @@
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
@@ -12042,7 +12042,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -12058,17 +12058,17 @@
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - självständigt och med stöd av verksamma lärare planera, genomföra, diskutera o…</t>
         </is>
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
@@ -12091,12 +12091,12 @@
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G345" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>27 ord: - med utgångspunkt i praktikens didaktiska villkor och utifrån ett hållbarhetspe…</t>
+          <t>29 ord: - redogöra för naturlandskapets förändringar och för människors utnyttjande av r…</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
@@ -12141,7 +12141,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -12151,23 +12151,23 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - med utgångspunkt i praktikens didaktiska villkor och utifrån ett hållbarhetspe…</t>
         </is>
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
@@ -12190,12 +12190,12 @@
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>27 ord: - identifiera och beakta grundläggande demokratiska värderingar samt olika jämst…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -12223,24 +12223,24 @@
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - identifiera och beakta grundläggande demokratiska värderingar samt olika jämst…</t>
         </is>
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -12250,30 +12250,30 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 1 för 0 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -12289,24 +12289,24 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>27 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
+          <t>0 lärandemål (minimum rekommenderat: 1 för 0 hp)</t>
         </is>
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -12327,19 +12327,19 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>38 ord: - identifiera och diskutera problem samt föreslå utvecklingsområden i den pedago…</t>
+          <t>27 ord: - självständigt och tillsammans med andra planera, genomföra, utvärdera och utve…</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -12360,19 +12360,19 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån egna erfarenheter i den pedagogiska verksamheten och tidigare forsknin…</t>
+          <t>38 ord: - identifiera och diskutera problem samt föreslå utvecklingsområden i den pedago…</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>34 ord: - använda det engelska språket för att i samarbete i internationellt blandade gr…</t>
+          <t>28 ord: - utifrån egna erfarenheter i den pedagogiska verksamheten och tidigare forsknin…</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>29 ord: - kritiskt reflektera över sin egen interkulturella kompetens och det interkultu…</t>
+          <t>34 ord: - använda det engelska språket för att i samarbete i internationellt blandade gr…</t>
         </is>
       </c>
       <c r="G355" s="2" t="inlineStr">
@@ -12438,7 +12438,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>GPG3KA</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -12459,19 +12459,19 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>28 ord: - diskutera och analysera den egna undervisningen, samt i samarbete med verksamm…</t>
+          <t>29 ord: - kritiskt reflektera över sin egen interkulturella kompetens och det interkultu…</t>
         </is>
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>GPG3KB</t>
+          <t>GPG3KA</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -12497,14 +12497,14 @@
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KA</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG3KB</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -12514,14 +12514,10 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2012-10-09</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>2013-05-15</t>
-        </is>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -12529,19 +12525,19 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
+          <t>28 ord: - diskutera och analysera den egna undervisningen, samt i samarbete med verksamm…</t>
         </is>
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -12551,12 +12547,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2013-03-15</t>
+          <t>2012-10-09</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2014-02-03</t>
+          <t>2013-05-15</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -12571,14 +12567,14 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -12603,32 +12599,36 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
+          <t>30 ord: - visa förmåga att, med krav på skriftlig och muntlig kommunikationsförmåga, pre…</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr"/>
+          <t>2013-03-15</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2014-02-03</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -12636,19 +12636,19 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
+          <t>31 ord: - visa fördjupad förmåga att, med krav på skriftlig och muntlig kommunikationsfö…</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -12669,19 +12669,19 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
+          <t>28 ord: - visa djupa kunskaper i förhållandet mellan mänskliga rättigheter, religioner o…</t>
         </is>
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -12702,12 +12702,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
+          <t>29 ord: - identifiera och analysera möjliga forskningsetiska problem i såväl det egna up…</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>29 ord: - redogöra för, samt på ett reflekterat sätt diskutera komplexiteten i identitet…</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
@@ -12747,7 +12747,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -12763,17 +12763,17 @@
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
@@ -12796,12 +12796,12 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12823,23 +12823,23 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
@@ -12862,12 +12862,12 @@
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
+          <t>29 ord: - redogöra för samt på ett reflekterat sätt diskutera komplexiteten i identitets…</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
+          <t>31 ord: - redogöra för och problematisera olika synsätt på relationen mellan religion oc…</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
@@ -12945,33 +12945,33 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>26 ord: - diskutera och reflektera över hur normkritiska aspekter kan bidra till en förd…</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
@@ -12994,12 +12994,12 @@
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -13021,23 +13021,23 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
@@ -13077,7 +13077,7 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -13093,24 +13093,24 @@
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>30 ord: - visa god kunskap om och förståelse av de lagar och den rättspraxis som gäller …</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -13120,23 +13120,23 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2007-04-04</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
+          <t>27 ord: - fått kunskap om fysiska och juridiska personers rättsliga ställning samt deras…</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
@@ -13176,7 +13176,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -13186,30 +13186,30 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2007-05-30</t>
+          <t>2007-04-04</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>29 ord: - fått grundläggande kunskaper om rättsprinciper av vikt för individen och föret…</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2009-05-13</t>
+          <t>2007-05-30</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -13230,19 +13230,19 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2009-06-08</t>
+          <t>2009-05-13</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -13263,19 +13263,19 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -13285,30 +13285,30 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2012-03-08</t>
+          <t>2009-06-08</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -13318,30 +13318,30 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2014-01-30</t>
+          <t>2012-03-08</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2014-01-30</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -13362,19 +13362,19 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
+          <t>27 ord: -  redogöra för de centrala socialrättsliga reglerna och andra rättsregler av sä…</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
+          <t>26 ord: - _förklara_ väsentliga aspekter av folkrätten; detta inbegriper förmågan att ku…</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -13428,19 +13428,19 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>33 ord: - _förklara_ väsentliga aspekter av den Europeiska unionen, EU-rätten och den EU…</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
@@ -13506,7 +13506,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -13527,19 +13527,19 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>32 ord: - visa grundläggande färdighet i att skriftligt och muntligt tillämpa principer …</t>
         </is>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr">
@@ -13605,7 +13605,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -13615,34 +13615,30 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>2015-08-24</t>
-        </is>
-      </c>
+          <t>2022-02-21</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>33 ord: - visa förmåga att tillämpa principer för god vetenskaplig framställning och rap…</t>
         </is>
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -13652,27 +13648,27 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2011-04-19</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2016-06-28</t>
+          <t>2015-08-24</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13700,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
+          <t>26 ord: - förstå samt problematisera hur EU använder sig av soft power och normer såsom …</t>
         </is>
       </c>
       <c r="G393" s="2" t="inlineStr">
@@ -13716,7 +13712,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>SK1060</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -13726,10 +13722,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr"/>
+          <t>2011-04-19</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2016-06-28</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -13737,19 +13737,19 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
+          <t>30 ord: - förstå och problematisera hur EU interagerar med andra stora aktörer såsom USA…</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>SK1064</t>
+          <t>SK1060</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2015-09-03</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -13770,19 +13770,19 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>28 ord: - utifrån centrala teorier inom ämnet internationelIa relationer (IR), förstå de…</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1060</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>SK1065</t>
+          <t>SK1064</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1064</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
+          <t>29 ord: - visa kunskap om olika sätt att förstå och använda säkerhetsbegreppet, både avs…</t>
         </is>
       </c>
       <c r="G397" s="2" t="inlineStr">
@@ -13848,7 +13848,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>SK2009</t>
+          <t>SK1065</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2015-09-03</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -13869,19 +13869,19 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
+          <t>26 ord: - visa fördjupad kunskap om olika aktörer och deras roller i olika internationel…</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1065</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>SK2009</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2015-02-13</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -13902,19 +13902,19 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
+          <t>27 ord: - uppvisa kunskap om utrikespolitikens förutsättningar och praktik i relationen …</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2009</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>SK2016</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -13935,52 +13935,52 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
+          <t>29 ord: - återge och problematisera teorier och modeller om väpnade konflikters och hybr…</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>SK2016</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2015-09-17</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - visa kunskap och förståelse inom en fördjupad del av huvudområdet statsvetensk…</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2016</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -14001,19 +14001,19 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -14034,19 +14034,19 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -14067,19 +14067,19 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -14105,14 +14105,14 @@
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -14122,14 +14122,10 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>2013-08-19</t>
-        </is>
-      </c>
+          <t>2023-03-13</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -14137,19 +14133,19 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -14159,10 +14155,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr"/>
+          <t>2013-03-14</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2013-08-19</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -14170,52 +14170,52 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>ATR2BB</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>ATR2BB</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -14236,19 +14236,19 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
+          <t>26 ord: - effektivt presentera och diskutera forskningsdesign, metoder, resultat och imp…</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -14269,19 +14269,19 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
+          <t>27 ord: - kritiskt reflektera över hur kunskap som förvärvats i kursen bidrar till breda…</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -14291,34 +14291,30 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2008-01-22</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
+          <t>2019-05-22</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>27 ord: - Diskutera och visa förståelse för de tre dimensionerna ekologisk, social och e…</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -14328,12 +14324,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2009-09-02</t>
+          <t>2008-01-22</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2012-03-27</t>
+          <t>2009-08-26</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -14348,14 +14344,14 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -14365,34 +14361,34 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2013-02-01</t>
+          <t>2009-09-02</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2014-04-23</t>
+          <t>2012-03-27</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -14402,34 +14398,34 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2015-03-09</t>
+          <t>2014-04-23</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -14439,30 +14435,34 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2014-01-30</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>2013-03-14</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2015-03-09</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - visa på förmåga till ett reflekterande och självständigt förhållningssätt geno…</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -14472,63 +14472,63 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2014-01-30</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR3010</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>29 ord: - muntligt och skriftligt presentera och diskutera teoretiska ansatser, argument…</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -14549,19 +14549,19 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
@@ -14627,7 +14627,7 @@
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -14640,31 +14640,27 @@
           <t>2014-12-10</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>2023-03-06</t>
-        </is>
-      </c>
+      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
+          <t>27 ord: - visa kunskaper om och förståelse för politiska, sociala och ekonomiska förhåll…</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -14689,12 +14685,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 8 hp)</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
@@ -14721,12 +14717,12 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr">
@@ -14738,7 +14734,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -14758,17 +14754,17 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
+          <t>26 ord: - visa insikt i och förmåga att tillämpa synkrona och diakrona perspektiv i stud…</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
@@ -14795,12 +14791,12 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
+          <t>2 lärandemål (minimum rekommenderat: 4 för 9 hp)</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -14812,7 +14808,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -14822,10 +14818,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
+          <t>2014-12-10</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -14833,12 +14833,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>29 ord: - visa fördjupade kunskaper om och kritiskt förhållningssätt till politiska, soc…</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
+          <t>31 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
+          <t>27 ord: - genomföra en självständig vetenskaplig studie med krav på relevant och aktuell…</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
+          <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
+          <t>26 ord: - diskutera och visa förståelse för utvecklingen av den internationella hälsan m…</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
@@ -14977,7 +14977,7 @@
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>AS3006</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -14998,19 +14998,19 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
+          <t>26 ord: - redovisa och värdera olika strategier och förhållningssätt som kan förbättra d…</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -15026,24 +15026,24 @@
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
+          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>AS3011</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2016-05-03</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -15064,19 +15064,19 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7 hp)</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>AS4004</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -15092,17 +15092,17 @@
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
+          <t>3 lärandemål (minimum rekommenderat: 5 för 16 hp)</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
+          <t>35 ord: - visa på fördjupad kunskap inom något av de områden som förekommer inom Afrikan…</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
@@ -15163,17 +15163,50 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
+          <t>34 ord: - med högt ställda krav på självständighet, och inom givna tidsramar genomföra e…</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>AS4004</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2016-05-03</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
           <t>30 ord: - skriftligt såväl som muntligt presentera och argumentera för egna resultat sam…</t>
         </is>
       </c>
-      <c r="G436" s="2" t="inlineStr">
+      <c r="G437" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G436"/>
+  <autoFilter ref="A1:G437"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -16045,6 +16078,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId868"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A436" r:id="rId869"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A437" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId872"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
